--- a/geekpractice/workbook.xlsx
+++ b/geekpractice/workbook.xlsx
@@ -12,9 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Hello, Apache POI!</t>
+    <t>発注ID</t>
+  </si>
+  <si>
+    <t>商品</t>
+  </si>
+  <si>
+    <t>数量</t>
   </si>
 </sst>
 </file>
@@ -59,12 +65,194 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
+      <c r="A1" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B1" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C1" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B12" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="B14" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="B16" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="B17" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>5.0</v>
       </c>
     </row>
   </sheetData>
